--- a/data/export/2026-10-29-浦东78路.xlsx
+++ b/data/export/2026-10-29-浦东78路.xlsx
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/16</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/16</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/16</t>
         </is>
       </c>
     </row>
@@ -945,22 +945,22 @@
       <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A51582D</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>06:50</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1012,7 +1012,7 @@
       <c r="T5" s="2" t="inlineStr"/>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -1048,7 +1048,1450 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-29-浦东78路.xlsx
+++ b/data/export/2026-10-29-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC18"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1492,7 +1492,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1603,7 +1603,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1714,7 +1714,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1825,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2047,7 +2047,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2158,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2380,7 +2380,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       <c r="T18" s="2" t="inlineStr"/>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2491,7 +2491,1006 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A53062D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-29-浦东78路.xlsx
+++ b/data/export/2026-10-29-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2832,22 +2832,22 @@
       <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>08:21</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2880,12 +2880,12 @@
       <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2899,7 +2899,7 @@
       <c r="T22" s="2" t="inlineStr"/>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -2943,22 +2943,22 @@
       <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A30260D</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2991,12 +2991,12 @@
       <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3010,7 +3010,7 @@
       <c r="T23" s="2" t="inlineStr"/>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3054,7 +3054,7 @@
       <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A36930D</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -3102,12 +3102,12 @@
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3387,22 +3387,22 @@
       <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3454,7 +3454,7 @@
       <c r="T27" s="2" t="inlineStr"/>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
@@ -3489,6 +3489,1005 @@
       </c>
       <c r="AB27" s="2" t="inlineStr"/>
       <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
         </is>

--- a/data/export/2026-10-29-浦东78路.xlsx
+++ b/data/export/2026-10-29-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC36"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4386,22 +4386,22 @@
       <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A51582D</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       <c r="T36" s="2" t="inlineStr"/>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
@@ -4488,6 +4488,339 @@
       </c>
       <c r="AB36" s="2" t="inlineStr"/>
       <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
         </is>

--- a/data/export/2026-10-29-浦东78路.xlsx
+++ b/data/export/2026-10-29-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AC42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4719,22 +4719,22 @@
       <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4786,7 +4786,7 @@
       <c r="T39" s="2" t="inlineStr"/>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
@@ -4821,6 +4821,339 @@
       </c>
       <c r="AB39" s="2" t="inlineStr"/>
       <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
         </is>

--- a/data/export/2026-10-29-浦东78路.xlsx
+++ b/data/export/2026-10-29-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AC49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5052,22 +5052,22 @@
       <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5119,7 +5119,7 @@
       <c r="T42" s="2" t="inlineStr"/>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
@@ -5154,6 +5154,783 @@
       </c>
       <c r="AB42" s="2" t="inlineStr"/>
       <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr"/>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr"/>
+      <c r="AC49" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
         </is>

--- a/data/export/2026-10-29-浦东78路.xlsx
+++ b/data/export/2026-10-29-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC49"/>
+  <dimension ref="A1:AC54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -5936,6 +5936,561 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr"/>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr"/>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr"/>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr"/>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr"/>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-29-浦东78路.xlsx
+++ b/data/export/2026-10-29-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC54"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6491,6 +6491,561 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr"/>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-29-浦东78路.xlsx
+++ b/data/export/2026-10-29-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6032,7 +6032,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6659,7 +6659,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7046,6 +7046,450 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr"/>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr"/>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-29-浦东78路.xlsx
+++ b/data/export/2026-10-29-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC63"/>
+  <dimension ref="A1:AC73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -815,18 +815,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -887,7 +891,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -931,13 +935,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -998,7 +1006,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1037,18 +1045,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1121,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1148,7 +1160,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1220,7 +1232,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1259,7 +1271,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1331,7 +1343,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1442,7 +1454,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1486,13 +1498,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1569,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1592,7 +1608,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1664,7 +1680,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1703,7 +1719,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1775,7 +1791,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,7 +1902,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1925,18 +1941,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2017,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2108,7 +2128,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2219,7 +2239,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2258,7 +2278,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2330,7 +2350,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2369,7 +2389,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2441,7 +2461,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2552,7 +2572,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2591,7 +2611,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2663,7 +2683,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2702,18 +2722,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2798,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2813,18 +2837,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2913,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2924,7 +2952,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -2996,7 +3024,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3040,13 +3068,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3250,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3257,7 +3289,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3329,7 +3361,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3373,13 +3405,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3440,7 +3476,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3551,7 +3587,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3590,7 +3626,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3662,7 +3698,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3701,7 +3737,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3773,7 +3809,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3884,7 +3920,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3995,7 +4031,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4034,18 +4070,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB32" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4146,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4145,7 +4185,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4217,7 +4257,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4256,7 +4296,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4328,7 +4368,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4367,18 +4407,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB35" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -4439,7 +4483,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4478,18 +4522,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB36" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4550,7 +4598,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4594,13 +4642,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB37" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4661,7 +4713,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4700,7 +4752,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4772,7 +4824,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4816,13 +4868,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB39" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4883,7 +4939,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -4994,7 +5050,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5033,7 +5089,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5105,7 +5161,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5216,7 +5272,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5327,7 +5383,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5366,7 +5422,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5438,7 +5494,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5477,18 +5533,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB45" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5549,7 +5609,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5588,18 +5648,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB46" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -5660,7 +5724,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5699,18 +5763,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB47" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5771,7 +5839,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -5815,13 +5883,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB48" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5882,7 +5954,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -5926,13 +5998,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB49" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5993,7 +6069,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6104,7 +6180,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6215,7 +6291,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6326,7 +6402,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6365,7 +6441,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6404,32 +6480,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -6437,7 +6517,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6461,33 +6541,37 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB54" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6515,32 +6599,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6548,7 +6636,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6572,33 +6660,37 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB55" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -6626,32 +6718,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6659,7 +6755,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -6683,33 +6779,37 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB56" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6737,32 +6837,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6770,7 +6874,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -6794,17 +6898,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -6814,13 +6918,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB57" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6881,7 +6989,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -6959,32 +7067,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6992,7 +7104,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7016,17 +7128,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7036,13 +7148,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB59" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7103,7 +7219,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7214,7 +7330,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7325,7 +7441,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7436,7 +7552,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7490,6 +7606,1128 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr"/>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr"/>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A53062D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr"/>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr"/>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-29-浦东78路.xlsx
+++ b/data/export/2026-10-29-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC73"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,18 +704,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -776,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -891,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -930,7 +934,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -945,7 +949,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1010,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1060,7 +1064,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1125,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1232,7 +1236,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1271,18 +1275,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1351,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1382,18 +1390,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1466,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1493,7 +1505,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1508,7 +1520,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1581,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1680,7 +1692,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1791,7 +1803,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1830,18 +1842,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1918,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1956,7 +1972,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2017,7 +2033,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2056,7 +2072,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2128,7 +2144,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2167,18 +2183,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2239,7 +2259,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2278,18 +2298,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2374,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2461,7 +2485,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2500,18 +2524,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2600,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2616,13 +2644,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2715,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2798,7 +2830,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2852,7 +2884,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2913,7 +2945,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3024,7 +3056,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3063,7 +3095,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3078,7 +3110,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3282,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3289,18 +3321,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3361,7 +3397,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3400,7 +3436,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3415,7 +3451,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3512,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3515,18 +3551,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3627,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3698,7 +3738,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3809,7 +3849,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3848,7 +3888,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -3920,7 +3960,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3959,18 +3999,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB31" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4075,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4085,7 +4129,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4190,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4185,18 +4229,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB33" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4257,7 +4305,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4368,7 +4416,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4483,7 +4531,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4537,7 +4585,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4646,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4637,7 +4685,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4652,7 +4700,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4761,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4824,7 +4872,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4863,7 +4911,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -4878,7 +4926,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4939,7 +4987,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -4978,18 +5026,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB40" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5102,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5161,7 +5213,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5200,7 +5252,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5272,7 +5324,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5311,18 +5363,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB43" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5383,7 +5439,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5422,18 +5478,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB44" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5554,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5548,7 +5608,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5609,7 +5669,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5724,7 +5784,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5778,7 +5838,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5899,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -5878,7 +5938,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -5893,7 +5953,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5954,7 +6014,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -5993,7 +6053,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6008,7 +6068,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6069,7 +6129,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6108,18 +6168,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB50" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6180,7 +6244,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6219,7 +6283,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6291,7 +6355,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6330,18 +6394,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB52" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6402,7 +6470,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6441,18 +6509,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB53" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6517,7 +6589,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6571,7 +6643,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6708,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6755,7 +6827,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -6809,7 +6881,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6946,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -6913,7 +6985,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -6928,7 +7000,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6956,32 +7028,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6989,7 +7065,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7013,33 +7089,37 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB58" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -7104,7 +7184,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7143,7 +7223,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7158,7 +7238,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7219,7 +7299,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7258,7 +7338,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7297,32 +7377,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7330,7 +7414,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7354,33 +7438,37 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB61" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7408,32 +7496,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -7441,7 +7533,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7465,33 +7557,37 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB62" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7519,32 +7615,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7552,7 +7652,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7576,33 +7676,37 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB63" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7630,32 +7734,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7663,7 +7771,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7687,33 +7795,37 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB64" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7741,32 +7853,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -7774,7 +7890,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -7798,33 +7914,37 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB65" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7885,7 +8005,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -7963,32 +8083,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>07:41</t>
@@ -7996,7 +8120,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8020,17 +8144,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8040,13 +8164,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB67" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8107,7 +8235,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8161,7 +8289,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8222,7 +8350,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8333,7 +8461,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8444,7 +8572,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8559,7 +8687,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8613,7 +8741,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8802,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -8728,6 +8856,1037 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr"/>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-29-浦东78路.xlsx
+++ b/data/export/2026-10-29-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6355,7 +6355,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6470,7 +6470,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7890,7 +7890,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8005,7 +8005,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8044,7 +8044,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8687,7 +8687,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8802,7 +8802,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9143,7 +9143,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9258,7 +9258,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9373,7 +9373,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9714,7 +9714,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -9829,7 +9829,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -9887,6 +9887,232 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr"/>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A53062D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-29-浦东78路.xlsx
+++ b/data/export/2026-10-29-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC84"/>
+  <dimension ref="A1:AC91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,22 +819,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1049,22 +1049,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1164,18 +1164,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1240,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1351,7 +1355,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1405,7 +1409,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1470,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1505,22 +1509,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1585,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1692,7 +1696,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1731,18 +1735,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1811,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1857,7 +1865,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1926,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1957,22 +1965,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2041,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2144,7 +2152,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2198,7 +2206,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2267,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,7 +2382,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2413,18 +2421,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2497,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,7 +2612,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2654,7 +2666,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2727,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2754,22 +2766,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2830,7 +2842,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2869,22 +2881,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2957,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2984,18 +2996,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3072,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3110,7 +3126,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3298,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3397,7 +3413,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3436,22 +3452,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3512,7 +3528,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3566,7 +3582,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3627,7 +3643,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3666,18 +3682,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3758,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3849,7 +3869,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3960,7 +3980,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4014,7 +4034,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4075,7 +4095,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4114,22 +4134,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4210,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4305,7 +4325,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4344,18 +4364,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB34" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4440,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4455,22 +4479,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4555,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4570,22 +4594,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4670,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4700,7 +4724,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4785,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4800,18 +4824,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB38" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4872,7 +4900,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4911,22 +4939,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4987,7 +5015,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5041,7 +5069,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5130,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5141,18 +5169,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB41" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5213,7 +5245,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5324,7 +5356,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5378,7 +5410,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5439,7 +5471,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5554,7 +5586,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5593,22 +5625,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5669,7 +5701,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5708,22 +5740,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5816,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5823,22 +5855,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5899,7 +5931,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -5953,7 +5985,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6014,7 +6046,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6053,22 +6085,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6129,7 +6161,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6183,7 +6215,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6244,7 +6276,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6355,7 +6387,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6409,7 +6441,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6502,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6589,7 +6621,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6628,22 +6660,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6740,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6747,22 +6779,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6827,7 +6859,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -6866,22 +6898,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6978,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7000,7 +7032,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7097,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7184,7 +7216,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7223,22 +7255,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7299,7 +7331,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7414,7 +7446,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7468,7 +7500,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7533,7 +7565,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7587,7 +7619,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7652,7 +7684,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7706,7 +7738,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7771,7 +7803,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7890,7 +7922,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8005,7 +8037,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8120,7 +8152,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8174,7 +8206,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8202,32 +8234,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -8235,7 +8271,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8259,37 +8295,37 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8317,32 +8353,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -8350,7 +8390,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8374,33 +8414,37 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB69" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8428,32 +8472,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -8461,7 +8509,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8485,33 +8533,37 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB70" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8539,32 +8591,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8572,7 +8628,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8596,37 +8652,37 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8654,32 +8710,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -8687,7 +8747,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8711,37 +8771,37 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8769,32 +8829,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -8802,7 +8866,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -8826,33 +8890,37 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB73" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8913,7 +8981,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -8967,7 +9035,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -8995,32 +9063,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -9028,7 +9100,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9052,37 +9124,37 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9143,7 +9215,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9258,7 +9330,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9312,7 +9384,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9373,7 +9445,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9484,7 +9556,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9538,7 +9610,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9599,7 +9671,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9653,7 +9725,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9714,7 +9786,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -9829,7 +9901,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -9944,7 +10016,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10055,7 +10127,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10109,7 +10181,812 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
           <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-29-浦东78路.xlsx
+++ b/data/export/2026-10-29-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC91"/>
+  <dimension ref="A1:AC99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,22 +704,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1279,22 +1279,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1519,12 +1519,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1850,22 +1850,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2080,18 +2080,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2156,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2191,22 +2195,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2271,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2311,17 +2315,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2386,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2436,7 +2440,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2497,7 +2501,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2536,22 +2540,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2616,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2651,7 +2655,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2666,7 +2670,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2727,7 +2731,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2781,7 +2785,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2842,7 +2846,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2896,7 +2900,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2957,7 +2961,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2996,7 +3000,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3011,7 +3015,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3072,7 +3076,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3111,7 +3115,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3126,7 +3130,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3298,7 +3302,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3337,22 +3341,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3413,7 +3417,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3462,12 +3466,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3532,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3582,7 +3586,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3643,7 +3647,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3697,7 +3701,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3758,7 +3762,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3869,7 +3873,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3908,18 +3912,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB30" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3988,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4019,22 +4027,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4095,7 +4103,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4149,7 +4157,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4218,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4254,17 +4262,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4333,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4379,7 +4387,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4448,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4494,7 +4502,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4555,7 +4563,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4609,7 +4617,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4678,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4709,7 +4717,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4724,7 +4732,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -4785,7 +4793,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4824,7 +4832,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4839,7 +4847,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4900,7 +4908,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4949,12 +4957,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5015,7 +5023,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5069,7 +5077,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5138,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5184,7 +5192,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5245,7 +5253,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5284,18 +5292,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB42" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5356,7 +5368,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5395,22 +5407,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5483,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5515,17 +5527,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -5586,7 +5598,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5640,7 +5652,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5713,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5755,7 +5767,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5816,7 +5828,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5870,7 +5882,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5931,7 +5943,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -5970,7 +5982,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -5985,7 +5997,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -6046,7 +6058,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6095,12 +6107,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6161,7 +6173,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6215,7 +6227,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6276,7 +6288,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6315,18 +6327,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB51" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6387,7 +6403,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6426,22 +6442,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6502,7 +6518,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6546,17 +6562,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -6621,7 +6637,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6675,7 +6691,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6756,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6794,7 +6810,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6859,7 +6875,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -6913,7 +6929,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6994,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7017,7 +7033,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7032,7 +7048,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -7097,7 +7113,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7136,22 +7152,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7232,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7265,12 +7281,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7331,7 +7347,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7370,18 +7386,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB60" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7446,7 +7466,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7500,7 +7520,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7565,7 +7585,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7604,22 +7624,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7704,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7723,22 +7743,22 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7803,7 +7823,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7847,17 +7867,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -7922,7 +7942,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -7961,22 +7981,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8037,7 +8057,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8152,7 +8172,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8191,7 +8211,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8206,7 +8226,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8291,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8325,7 +8345,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8410,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8429,7 +8449,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8444,7 +8464,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8509,7 +8529,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8563,7 +8583,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8628,7 +8648,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8682,7 +8702,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8767,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8801,7 +8821,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8866,7 +8886,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -8920,7 +8940,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8981,7 +9001,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9020,7 +9040,7 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9035,7 +9055,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -9073,24 +9093,24 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -9100,7 +9120,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9149,12 +9169,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9182,32 +9202,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9215,7 +9239,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9239,37 +9263,37 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9330,7 +9354,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9384,7 +9408,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9412,32 +9436,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9445,7 +9473,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9469,33 +9497,37 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB78" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9523,32 +9555,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>110分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9556,7 +9592,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9580,37 +9616,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9638,32 +9674,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>106分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -9671,7 +9711,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9695,37 +9735,37 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9753,32 +9793,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>119分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9786,7 +9830,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -9810,17 +9854,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -9830,17 +9874,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -9868,32 +9912,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>116分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -9901,7 +9949,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -9925,37 +9973,37 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10064,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10127,7 +10175,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10166,7 +10214,7 @@
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
@@ -10181,7 +10229,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -10242,7 +10290,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10296,7 +10344,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -10357,7 +10405,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10396,7 +10444,7 @@
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA86" s="2" t="inlineStr">
@@ -10411,7 +10459,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -10472,7 +10520,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10526,7 +10574,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -10587,7 +10635,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10641,7 +10689,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10750,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10756,7 +10804,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -10817,7 +10865,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -10866,12 +10914,12 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -10932,7 +10980,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -10986,7 +11034,927 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>91.5</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A53062D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
           <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-29-浦东78路.xlsx
+++ b/data/export/2026-10-29-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:AC103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -824,17 +824,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1169,17 +1169,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1624,18 +1624,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1700,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1735,7 +1739,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1750,7 +1754,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1815,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1860,7 +1864,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1926,7 +1930,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1980,7 +1984,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2045,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2095,7 +2099,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2160,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2210,7 +2214,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2275,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2320,7 +2324,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2386,7 +2390,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2425,22 +2429,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2505,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2540,7 +2544,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2555,7 +2559,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2620,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2660,17 +2664,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2731,7 +2735,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2775,17 +2779,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2846,7 +2850,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2900,7 +2904,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2965,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3005,17 +3009,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3080,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3302,7 +3306,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3417,7 +3421,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3471,7 +3475,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3651,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3686,7 +3690,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3701,7 +3705,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3766,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3801,18 +3805,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB29" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3881,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3927,7 +3935,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3996,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4037,7 +4045,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4103,7 +4111,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4157,7 +4165,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4226,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4267,7 +4275,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4333,7 +4341,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4372,22 +4380,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4448,7 +4456,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4492,17 +4500,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4563,7 +4571,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4617,7 +4625,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4686,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4793,7 +4801,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4837,17 +4845,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4908,7 +4916,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4962,7 +4970,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5138,7 +5146,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5177,7 +5185,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5192,7 +5200,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5261,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5307,7 +5315,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5368,7 +5376,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5417,7 +5425,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5483,7 +5491,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5532,7 +5540,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5598,7 +5606,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5652,7 +5660,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5713,7 +5721,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5757,17 +5765,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5836,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5882,7 +5890,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5943,7 +5951,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6058,7 +6066,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6112,7 +6120,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6296,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6342,7 +6350,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6403,7 +6411,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6452,7 +6460,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6518,7 +6526,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6567,7 +6575,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6637,7 +6645,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6691,7 +6699,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6756,7 +6764,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6800,17 +6808,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6875,7 +6883,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -6929,7 +6937,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6994,7 +7002,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7113,7 +7121,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7152,7 +7160,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7167,7 +7175,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7232,7 +7240,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7286,7 +7294,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7347,7 +7355,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7401,7 +7409,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7585,7 +7593,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7639,7 +7647,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7704,7 +7712,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7753,7 +7761,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -7823,7 +7831,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7872,7 +7880,7 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -7942,7 +7950,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8057,7 +8065,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8096,18 +8104,22 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB66" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -8172,7 +8184,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8216,17 +8228,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8291,7 +8303,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8345,7 +8357,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8410,7 +8422,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8454,17 +8466,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8529,7 +8541,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8568,22 +8580,22 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8648,7 +8660,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8692,17 +8704,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8767,7 +8779,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8821,7 +8833,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8898,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -8925,7 +8937,7 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -8940,7 +8952,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9001,7 +9013,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9120,7 +9132,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9174,7 +9186,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9239,7 +9251,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9278,7 +9290,7 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9293,7 +9305,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9473,7 +9485,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9527,7 +9539,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9565,24 +9577,24 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>110分钟</t>
+          <t>112分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9592,7 +9604,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9641,7 +9653,7 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9711,7 +9723,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9765,7 +9777,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9803,12 +9815,12 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>119分钟</t>
+          <t>117分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
@@ -9830,7 +9842,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -9879,7 +9891,7 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -9949,7 +9961,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10031,32 +10043,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>110分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10064,7 +10080,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10088,33 +10104,37 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB83" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -10142,32 +10162,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>07:41</t>
@@ -10175,7 +10199,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10199,17 +10223,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10219,17 +10243,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10314,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10344,7 +10368,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -10372,32 +10396,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10405,7 +10433,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10429,17 +10457,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10449,17 +10477,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10487,32 +10515,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>107分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -10520,7 +10552,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10544,37 +10576,37 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -10635,7 +10667,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10689,7 +10721,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -10717,32 +10749,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10750,7 +10786,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10774,17 +10810,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -10794,17 +10830,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -10865,7 +10901,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -10919,7 +10955,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -10980,7 +11016,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11019,7 +11055,7 @@
       </c>
       <c r="Z91" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA91" s="2" t="inlineStr">
@@ -11034,7 +11070,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -11095,7 +11131,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11210,7 +11246,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11264,7 +11300,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -11325,7 +11361,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11364,7 +11400,7 @@
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -11379,7 +11415,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -11440,7 +11476,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11494,7 +11530,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -11555,7 +11591,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11604,7 +11640,7 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
@@ -11670,7 +11706,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11714,17 +11750,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -11785,7 +11821,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -11900,7 +11936,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -11944,17 +11980,477 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB99" s="2" t="inlineStr">
-        <is>
-          <t>86.0</t>
-        </is>
-      </c>
-      <c r="AC99" s="2" t="inlineStr">
-        <is>
-          <t>7/18</t>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>96.5</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-29-浦东78路.xlsx
+++ b/data/export/2026-10-29-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC103"/>
+  <dimension ref="A1:AC106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -939,17 +939,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1169,17 +1169,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1279,22 +1279,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1514,17 +1514,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1744,17 +1744,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1859,17 +1859,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2664,17 +2664,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3009,17 +3009,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3080,7 +3080,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3124,17 +3124,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3345,22 +3345,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3465,17 +3465,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3695,17 +3695,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4040,17 +4040,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4730,17 +4730,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4801,7 +4801,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4845,17 +4845,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4960,17 +4960,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5085,7 +5085,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5190,17 +5190,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5420,17 +5420,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -5995,17 +5995,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6066,7 +6066,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6110,17 +6110,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6455,17 +6455,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7046,17 +7046,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7284,17 +7284,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7528,7 +7528,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7756,17 +7756,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7950,7 +7950,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -7989,22 +7989,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8065,7 +8065,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8184,7 +8184,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8228,17 +8228,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8422,7 +8422,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8466,17 +8466,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8541,7 +8541,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8595,7 +8595,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8898,7 +8898,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -8942,17 +8942,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -9013,7 +9013,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9057,17 +9057,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9132,7 +9132,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9176,17 +9176,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9251,7 +9251,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9420,7 +9420,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -9485,7 +9485,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9539,7 +9539,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9604,7 +9604,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9648,17 +9648,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9777,7 +9777,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9961,7 +9961,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10000,22 +10000,22 @@
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -10080,7 +10080,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10119,7 +10119,7 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10243,17 +10243,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -10433,7 +10433,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10477,17 +10477,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10552,7 +10552,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -10868,32 +10868,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10901,7 +10905,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -10925,17 +10929,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -10945,17 +10949,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10983,32 +10987,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -11016,7 +11024,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11040,17 +11048,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11060,17 +11068,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -11098,32 +11106,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11131,7 +11143,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11155,17 +11167,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11175,17 +11187,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -11246,7 +11258,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11300,7 +11312,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11373,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11476,7 +11488,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11530,7 +11542,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -11558,32 +11570,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11591,7 +11607,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11615,17 +11631,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11635,17 +11651,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -11673,32 +11689,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>07:41</t>
@@ -11706,7 +11726,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11730,17 +11750,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11750,17 +11770,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -11788,32 +11808,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -11821,7 +11845,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -11845,37 +11869,37 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -11903,32 +11927,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -11936,7 +11964,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -11960,17 +11988,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -11980,17 +12008,17 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -12051,7 +12079,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12090,7 +12118,7 @@
       </c>
       <c r="Z100" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA100" s="2" t="inlineStr">
@@ -12166,7 +12194,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12210,17 +12238,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -12281,7 +12309,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12320,7 +12348,7 @@
       </c>
       <c r="Z102" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA102" s="2" t="inlineStr">
@@ -12335,7 +12363,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -12396,7 +12424,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12454,6 +12482,351 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>94.3</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>96.5</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-29-浦东78路.xlsx
+++ b/data/export/2026-10-29-浦东78路.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1629,17 +1629,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1744,17 +1744,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2549,12 +2549,12 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3014,12 +3014,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3695,17 +3695,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3810,17 +3810,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4385,17 +4385,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4801,7 +4801,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4850,12 +4850,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5190,17 +5190,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5315,7 +5315,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -6465,7 +6465,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6580,7 +6580,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7165,12 +7165,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7409,7 +7409,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7885,7 +7885,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -7950,7 +7950,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8004,7 +8004,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8065,7 +8065,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8109,17 +8109,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8238,7 +8238,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8422,7 +8422,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8471,12 +8471,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8541,7 +8541,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8585,17 +8585,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8898,7 +8898,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -8942,17 +8942,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9186,7 +9186,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9251,7 +9251,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9295,12 +9295,12 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9539,7 +9539,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9777,7 +9777,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9896,7 +9896,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -9961,7 +9961,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10015,7 +10015,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -10080,7 +10080,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10124,17 +10124,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -10253,7 +10253,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10433,7 +10433,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10482,12 +10482,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -10552,7 +10552,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10596,17 +10596,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -10959,7 +10959,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -11024,7 +11024,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11068,17 +11068,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -11312,7 +11312,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -11373,7 +11373,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11417,12 +11417,12 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
@@ -11542,7 +11542,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -11661,7 +11661,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -11780,7 +11780,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -11845,7 +11845,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -11937,24 +11937,24 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:47</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -11964,7 +11964,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -12046,32 +12046,36 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:47</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -12079,7 +12083,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12103,17 +12107,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12123,17 +12127,17 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -12161,32 +12165,36 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -12194,7 +12202,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12218,17 +12226,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12238,17 +12246,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -12276,32 +12284,36 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -12309,7 +12321,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12333,17 +12345,17 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
@@ -12353,17 +12365,17 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -12391,32 +12403,36 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:44</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12424,7 +12440,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12448,17 +12464,17 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr">
@@ -12468,12 +12484,12 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
@@ -12539,7 +12555,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12593,7 +12609,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -12654,7 +12670,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12698,17 +12714,17 @@
       </c>
       <c r="AA105" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -12769,7 +12785,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -12813,17 +12829,17 @@
       </c>
       <c r="AA106" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
